--- a/HPE/excel/HPE_financial_analysis.xlsx
+++ b/HPE/excel/HPE_financial_analysis.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
     <numFmt numFmtId="168" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,9 @@
       <b val="1"/>
       <color rgb="00135927"/>
     </font>
+    <font>
+      <color rgb="005A6660"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -88,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,6 +113,8 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7507,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7521,6 +7526,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7531,9 +7538,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Regressions with Newey-West HAC errors; SARIMA revenue baseline; return diagnostics — see code/statistical_analysis.py</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Quarterly regressions use Newey-West HAC errors with t-distribution p-values, joint lag tests and robustness variants; SARIMA revenue baseline with Diebold-Mariano backtest tests and eight alternative baselines; return diagnostics; tests of descriptive claims — see code/statistical_analysis.py and code/business_model_analysis.py</t>
         </is>
       </c>
     </row>
@@ -7545,37 +7552,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>coef</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>std_err_hac</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>ci_low</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>ci_high</t>
         </is>
@@ -7597,13 +7604,13 @@
         <v>-1.431807868699378</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.1521988147187674</v>
+        <v>0.162889303407039</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>-0.1044414092848131</v>
+        <v>-0.1070669589467301</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0.0162632899403624</v>
+        <v>0.0188888396022794</v>
       </c>
     </row>
     <row r="7">
@@ -7622,13 +7629,13 @@
         <v>1.497988744419454</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.1341361748276572</v>
+        <v>0.144943108788437</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>-0.0302351243127062</v>
+        <v>-0.035815548398303</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>0.2263143596186213</v>
+        <v>0.2318947837042181</v>
       </c>
     </row>
     <row r="8">
@@ -7647,13 +7654,13 @@
         <v>1.736844597603603</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>0.08241460470124461</v>
+        <v>0.0930274101874092</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>-0.0153020646771691</v>
+        <v>-0.0211497887370944</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.2535360319862658</v>
+        <v>0.259383756046191</v>
       </c>
     </row>
     <row r="9">
@@ -7672,13 +7679,13 @@
         <v>-0.7240150621608353</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.4690564880565837</v>
+        <v>0.4748570944722802</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>-0.097671965032048</v>
+        <v>-0.1007748448168438</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.0449770873123636</v>
+        <v>0.0480799670971595</v>
       </c>
     </row>
     <row r="10">
@@ -7697,13 +7704,13 @@
         <v>3.474416983457685</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>0.0005119647558711</v>
+        <v>0.0016303625351288</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.06724452438811961</v>
+        <v>0.06345857091478251</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.2412966026664605</v>
+        <v>0.2450825561397976</v>
       </c>
     </row>
     <row r="13">
@@ -7714,37 +7721,37 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>coef</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>std_err_hac</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>ci_low</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>ci_high</t>
         </is>
@@ -7766,13 +7773,13 @@
         <v>-1.377074647249951</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.1684891701478369</v>
+        <v>0.1806957013206696</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>-0.1015200394198074</v>
+        <v>-0.1045493163343501</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>0.017732772984811</v>
+        <v>0.0207620498993537</v>
       </c>
     </row>
     <row r="16">
@@ -7791,13 +7798,13 @@
         <v>1.284030535277367</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.1991312714589259</v>
+        <v>0.2109042502051735</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>-0.0441324575693156</v>
+        <v>-0.0506337934795998</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.2118040624518595</v>
+        <v>0.2183053983621437</v>
       </c>
     </row>
     <row r="17">
@@ -7816,13 +7823,13 @@
         <v>1.80729029094644</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.07071702907055651</v>
+        <v>0.0827667854605338</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>-0.0106189738246577</v>
+        <v>-0.0175447231700068</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.2620253273540667</v>
+        <v>0.2689510766994158</v>
       </c>
     </row>
     <row r="18">
@@ -7841,54 +7848,54 @@
         <v>-0.7079552657162282</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>0.4789730379333574</v>
+        <v>0.4855216699744317</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>-0.0997489617720583</v>
+        <v>-0.1034718854689496</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>0.0468104759243537</v>
+        <v>0.050533399621245</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>R2: change in HPE gross margin (pp) on change in Micron gross margin (pp)</t>
+          <t>R1c: same as R1 with capex lags 0–4 (robustness)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>coef</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>std_err_hac</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>ci_low</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="18" t="inlineStr">
         <is>
           <t>ci_high</t>
         </is>
@@ -7901,1118 +7908,2589 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>-0.2349226231175515</v>
+        <v>-0.0215376618721219</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>0.730397888688027</v>
+        <v>0.0412740667717342</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>-0.3216365035494967</v>
+        <v>-0.5218206868549153</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.7477280862788007</v>
+        <v>0.6062125594241515</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>-1.66647617933018</v>
+        <v>-0.1063777211739332</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>1.196630933095077</v>
+        <v>0.0633023974296892</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>micron_gm_change_lag0</t>
+          <t>capex_yoy_lag0</t>
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>-0.0459467470967387</v>
+        <v>0.026772421129934</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.0148778951864202</v>
+        <v>0.08783305081947509</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>-3.088255866910296</v>
+        <v>0.3048103291431815</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>0.0020133504177263</v>
+        <v>0.7629372466007859</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>-0.0751068858278842</v>
+        <v>-0.1537710005153124</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>-0.0167866083655932</v>
+        <v>0.2073158427751804</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>micron_gm_change_lag1</t>
+          <t>capex_yoy_lag1</t>
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>0.009125743544119699</v>
+        <v>0.1404561663569072</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.0253075598251946</v>
+        <v>0.0707719150684462</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.3605935778539471</v>
+        <v>1.984631420826562</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>0.7184032909042917</v>
+        <v>0.0578322566052006</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>-0.0404761622498545</v>
+        <v>-0.0050175884954169</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>0.0587276493380939</v>
+        <v>0.2859299212092313</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>micron_gm_change_lag2</t>
+          <t>capex_yoy_lag2</t>
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>-0.0231283866821922</v>
+        <v>0.0418551703193064</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>0.030961817046062</v>
+        <v>0.030715289243858</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>-0.7469970721609812</v>
+        <v>1.362681952528772</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>0.4550653281647505</v>
+        <v>0.1846701963418545</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>-0.0838124329883921</v>
+        <v>-0.0212810109378744</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>0.0375556596240075</v>
+        <v>0.1049913515764872</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>capex_yoy_lag3</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>-0.0629044398186045</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>0.0492047562084144</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>-1.278421938565511</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>0.2123955642653671</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>-0.1640462647262459</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>0.0382373850890368</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>capex_yoy_lag4</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="n">
+        <v>-0.0521426473608642</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>0.0736108525592257</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>-0.7083554333093937</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>0.4850273948709621</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>-0.2034519217999525</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>0.0991666270782241</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>juniper_dummy</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>6.813126155328705</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>2.022308695508809</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>3.368984255697192</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>0.000754457382617</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>2.84947394650926</v>
-      </c>
-      <c r="G27" s="16" t="n">
-        <v>10.77677836414815</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>SARIMA model selection by AICc (top 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>seasonal</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>aicc</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>aic</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>converged</t>
-        </is>
+      <c r="B29" s="16" t="n">
+        <v>0.1841690954119375</v>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>0.047485077804164</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>3.878462538725951</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0.0006413640387087</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>0.086562120089231</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>0.2817760707346439</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>(0, 0, 1)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>(0, 0, 0)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="n">
-        <v>-80.76052032075344</v>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>-81.68359724383036</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>R2: change in HPE gross margin (pp) on change in Micron gross margin (pp), lags 0–2, Juniper dummy</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>(1, 0, 0)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>(0, 0, 0)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="n">
-        <v>-79.2250694206604</v>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>-80.14814634373732</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>coef</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>std_err_hac</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>ci_low</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>ci_high</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>(1, 0, 0)</t>
-        </is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>-0.2349226231175515</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>-79.04331614941496</v>
+        <v>0.730397888688027</v>
       </c>
       <c r="D34" s="16" t="n">
-        <v>-81.54331614941496</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+        <v>-0.3216365035494967</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0.7502996638063358</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>-1.73627698523839</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>1.266431739003287</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>(0, 0, 0)</t>
-        </is>
+          <t>micron_gm_change_lag0</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>-0.0459467470967387</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>-78.00979528579686</v>
+        <v>0.0148778951864202</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>-79.60979528579685</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+        <v>-3.088255866910296</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>0.0047453737442789</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>-0.0765286986374686</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>-0.0153647955560088</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>(2, 1, 0)</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>(0, 0, 0)</t>
-        </is>
+          <t>micron_gm_change_lag1</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="n">
+        <v>0.009125743544119699</v>
       </c>
       <c r="C36" s="16" t="n">
-        <v>-77.66229737274683</v>
+        <v>0.0253075598251946</v>
       </c>
       <c r="D36" s="16" t="n">
-        <v>-78.58537429582375</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+        <v>0.3605935778539471</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0.7213164607029759</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <v>-0.0428946906967834</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>0.0611461777850229</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>(1, 0, 0)</t>
-        </is>
+          <t>micron_gm_change_lag2</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="n">
+        <v>-0.0231283866821922</v>
       </c>
       <c r="C37" s="16" t="n">
-        <v>-77.10192681009327</v>
+        <v>0.030961817046062</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>-79.60192681009327</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+        <v>-0.7469970721609812</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>0.4617676930174811</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>-0.08677131309424729</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>0.0405145397298628</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>(1, 0, 0)</t>
-        </is>
+          <t>juniper_dummy</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="n">
+        <v>6.813126155328705</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>-76.84608108904516</v>
+        <v>2.022308695508809</v>
       </c>
       <c r="D38" s="16" t="n">
-        <v>-77.2905255334896</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>(1, 1, 1)</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>(1, 0, 0)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>-76.43902131534753</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>-78.03902131534753</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>True</t>
+        <v>3.368984255697192</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0.0023623056108195</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>2.656211097686885</v>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>10.97004121297052</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>R2b: same without the Juniper dummy (robustness)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>One-step rolling backtest, last 8 pre-Juniper quarters ($m)</t>
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>coef</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>std_err_hac</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>ci_low</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>ci_high</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>quarter</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>arima</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>random_walk</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>seasonal_naive</t>
-        </is>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="n">
+        <v>0.859801866392325</v>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>0.9720973085400224</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>0.8844812744967351</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0.3842453494970458</v>
+      </c>
+      <c r="F43" s="16" t="n">
+        <v>-1.134777056258443</v>
+      </c>
+      <c r="G43" s="16" t="n">
+        <v>2.854380789043093</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2023Q2</t>
+          <t>micron_gm_change_lag0</t>
         </is>
       </c>
       <c r="B44" s="16" t="n">
-        <v>7001.999999999995</v>
+        <v>-0.0065130766446092</v>
       </c>
       <c r="C44" s="16" t="n">
-        <v>6979.352717584006</v>
+        <v>0.0427930288863302</v>
       </c>
       <c r="D44" s="16" t="n">
-        <v>6972.999999999995</v>
+        <v>-0.1521994776745002</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>6950.999999999997</v>
+        <v>0.8801612396341421</v>
+      </c>
+      <c r="F44" s="16" t="n">
+        <v>-0.09431711920620391</v>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>0.0812909659169853</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2023Q3</t>
+          <t>micron_gm_change_lag1</t>
         </is>
       </c>
       <c r="B45" s="16" t="n">
-        <v>7350.999999999995</v>
+        <v>-0.0282845543518557</v>
       </c>
       <c r="C45" s="16" t="n">
-        <v>7188.721388372651</v>
+        <v>0.0325392002918729</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>7001.999999999995</v>
+        <v>-0.8692455284133124</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>7870.999999999994</v>
+        <v>0.3923747081698009</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>-0.0950494784925847</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>0.0384803697888733</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>micron_gm_change_lag2</t>
         </is>
       </c>
       <c r="B46" s="16" t="n">
-        <v>6754.999999999996</v>
+        <v>0.013112258364659</v>
       </c>
       <c r="C46" s="16" t="n">
-        <v>7288.72706993437</v>
+        <v>0.025113836063346</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>7350.999999999995</v>
+        <v>0.5221129233935138</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>7809.000000000002</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2024Q1</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n">
-        <v>7204.000000000001</v>
-      </c>
-      <c r="C47" s="16" t="n">
-        <v>6814.331107889596</v>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>6754.999999999996</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>6972.999999999995</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2024Q2</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>7709.999999999999</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>7398.184677051378</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>7204.000000000001</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>7001.999999999995</v>
+        <v>0.605849242868701</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>-0.0384170768559973</v>
+      </c>
+      <c r="G46" s="16" t="n">
+        <v>0.0646415935853154</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2024Q3</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n">
-        <v>8458.000000000005</v>
-      </c>
-      <c r="C49" s="16" t="n">
-        <v>7360.645997958367</v>
-      </c>
-      <c r="D49" s="16" t="n">
-        <v>7709.999999999999</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>7350.999999999995</v>
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>Joint tests: do the lag coefficients sum to zero? (t-test on the sum)</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2024Q4</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>7854.000000000006</v>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>7872.81529545054</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>8458.000000000005</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>6754.999999999996</v>
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>lags</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>coef</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>std_err</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
+        <is>
+          <t>ci_low</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="inlineStr">
+        <is>
+          <t>ci_high</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025Q1</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n">
-        <v>7626.999999999999</v>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>7235.230854923676</v>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>34</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>capex_yoy_lag0, capex_yoy_lag1, capex_yoy_lag2</t>
+        </is>
       </c>
       <c r="D51" s="16" t="n">
-        <v>7854.000000000006</v>
+        <v>0.1908091624476637</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>7204.000000000001</v>
+        <v>0.08303497740005179</v>
+      </c>
+      <c r="F51" s="16" t="n">
+        <v>2.297937187703078</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>0.0289696713794479</v>
+      </c>
+      <c r="H51" s="16" t="n">
+        <v>0.0209835653352586</v>
+      </c>
+      <c r="I51" s="16" t="n">
+        <v>0.3606347595600687</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>R1b</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>29</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>capex_yoy_lag0, capex_yoy_lag1, capex_yoy_lag2</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>0.183069736282124</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>0.08117934731787479</v>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>2.255126979098218</v>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>0.0331298989218426</v>
+      </c>
+      <c r="H52" s="16" t="n">
+        <v>0.0158777407936111</v>
+      </c>
+      <c r="I52" s="16" t="n">
+        <v>0.3502617317706369</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>R1c</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>33</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>capex_yoy_lag0, capex_yoy_lag1, capex_yoy_lag2, capex_yoy_lag3, capex_yoy_lag4</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>0.09403667062667879</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>0.1229365447210028</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>0.7649203972674645</v>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>0.4512065580242902</v>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>-0.1586630161323782</v>
+      </c>
+      <c r="I53" s="16" t="n">
+        <v>0.3467363573857359</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>Counterfactual forecast vs actual ($m)</t>
-        </is>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>31</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>micron_gm_change_lag0, micron_gm_change_lag1, micron_gm_change_lag2</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="n">
+        <v>-0.0599493902348113</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>0.0226534262503429</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>-2.646371880893893</v>
+      </c>
+      <c r="G54" s="16" t="n">
+        <v>0.0136291686064308</v>
+      </c>
+      <c r="H54" s="16" t="n">
+        <v>-0.1065141747785165</v>
+      </c>
+      <c r="I54" s="16" t="n">
+        <v>-0.013384605691106</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>R2b</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>31</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>micron_gm_change_lag0, micron_gm_change_lag1, micron_gm_change_lag2</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>-0.0216853726318059</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0.0407708317445249</v>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>-0.5318844797596756</v>
+      </c>
+      <c r="G55" s="16" t="n">
+        <v>0.5991556344649487</v>
+      </c>
+      <c r="H55" s="16" t="n">
+        <v>-0.1053402093875052</v>
+      </c>
+      <c r="I55" s="16" t="n">
+        <v>0.0619694641238934</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>R2 decomposition of the latest quarters (pp): memory part, Juniper part, constant, fitted, unexplained</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>calendar_quarter</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
         <is>
           <t>fiscal_quarter</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>forecast</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>lo80</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>hi80</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>lo95</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>hi95</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>actual_vs_forecast</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>outside_95</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2025Q2</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Q3 FY25</t>
-        </is>
-      </c>
-      <c r="C56" s="16" t="n">
-        <v>7478.837167330837</v>
-      </c>
-      <c r="D56" s="16" t="n">
-        <v>6963.582091932272</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>8032.21741871197</v>
-      </c>
-      <c r="F56" s="16" t="n">
-        <v>6705.351696791737</v>
-      </c>
-      <c r="G56" s="16" t="n">
-        <v>8341.546857596002</v>
-      </c>
-      <c r="H56" s="16" t="n">
-        <v>9135.999999999998</v>
-      </c>
-      <c r="I56" s="16" t="n">
-        <v>0.2215802798739894</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2025Q3</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Q4 FY25</t>
-        </is>
-      </c>
-      <c r="C57" s="16" t="n">
-        <v>7263.916692435499</v>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>6684.471401746357</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>7893.591361742989</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>6396.68375475038</v>
-      </c>
-      <c r="G57" s="16" t="n">
-        <v>8248.725079688129</v>
-      </c>
-      <c r="H57" s="16" t="n">
-        <v>9679.000000000007</v>
-      </c>
-      <c r="I57" s="16" t="n">
-        <v>0.3324767353237308</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2025Q4</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Q1 FY26</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="n">
-        <v>7263.916692435499</v>
-      </c>
-      <c r="D58" s="16" t="n">
-        <v>6684.471401746357</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>7893.591361742989</v>
-      </c>
-      <c r="F58" s="16" t="n">
-        <v>6396.68375475038</v>
-      </c>
-      <c r="G58" s="16" t="n">
-        <v>8248.725079688129</v>
-      </c>
-      <c r="H58" s="16" t="n">
-        <v>9301.000000000004</v>
-      </c>
-      <c r="I58" s="16" t="n">
-        <v>0.2804386935888023</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026Q1</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Q2 FY26</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="n">
-        <v>7263.916692435499</v>
-      </c>
-      <c r="D59" s="16" t="n">
-        <v>6684.471401746357</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>7893.591361742989</v>
-      </c>
-      <c r="F59" s="16" t="n">
-        <v>6396.68375475038</v>
-      </c>
-      <c r="G59" s="16" t="n">
-        <v>8248.725079688129</v>
-      </c>
-      <c r="H59" s="16" t="n">
-        <v>10678</v>
-      </c>
-      <c r="I59" s="16" t="n">
-        <v>0.4700058456231821</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>hpe_gross_margin</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>micron_gross_margin</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>hpe_gm_yoy_change_pp</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>micron_gm_change_pp</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>memory_part_pp</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>juniper_part_pp</t>
+        </is>
+      </c>
+      <c r="I59" s="18" t="inlineStr">
+        <is>
+          <t>constant_pp</t>
+        </is>
+      </c>
+      <c r="J59" s="18" t="inlineStr">
+        <is>
+          <t>fitted_pp</t>
+        </is>
+      </c>
+      <c r="K59" s="18" t="inlineStr">
+        <is>
+          <t>unexplained_pp</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2025Q1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Q3 FY26</t>
+          <t>Q2 FY25</t>
         </is>
       </c>
       <c r="C60" s="16" t="n">
-        <v>7263.916692435499</v>
+        <v>0.2843844237577029</v>
       </c>
       <c r="D60" s="16" t="n">
-        <v>6684.471401746357</v>
+        <v>0.3679374146280889</v>
       </c>
       <c r="E60" s="16" t="n">
-        <v>7893.591361742989</v>
+        <v>-4.543234470426272</v>
       </c>
       <c r="F60" s="16" t="n">
-        <v>6396.68375475038</v>
+        <v>18.26695574852318</v>
       </c>
       <c r="G60" s="16" t="n">
-        <v>8248.725079688129</v>
+        <v>-1.549427007032967</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>12213</v>
+        <v>0</v>
       </c>
       <c r="I60" s="16" t="n">
-        <v>0.6813243484356557</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+        <v>-0.2349226231175515</v>
+      </c>
+      <c r="J60" s="16" t="n">
+        <v>-1.784349630150518</v>
+      </c>
+      <c r="K60" s="16" t="n">
+        <v>-2.758884840275754</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026Q3</t>
+          <t>2025Q2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Q4 FY26</t>
+          <t>Q3 FY25</t>
         </is>
       </c>
       <c r="C61" s="16" t="n">
-        <v>7263.916692435499</v>
+        <v>0.2924693520140105</v>
       </c>
       <c r="D61" s="16" t="n">
-        <v>6684.471401746357</v>
+        <v>0.3771637458337813</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>7893.591361742989</v>
+        <v>-2.387306043735138</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>6396.68375475038</v>
+        <v>10.81870904234157</v>
       </c>
       <c r="G61" s="16" t="n">
-        <v>8248.725079688129</v>
+        <v>-1.236637786168472</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v/>
+        <v>6.813126155328705</v>
       </c>
       <c r="I61" s="16" t="n">
-        <v/>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+        <v>-0.2349226231175515</v>
+      </c>
+      <c r="J61" s="16" t="n">
+        <v>5.341565746042681</v>
+      </c>
+      <c r="K61" s="16" t="n">
+        <v>-7.728871789777819</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026Q4</t>
+          <t>2025Q3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Q1 FY27</t>
+          <t>Q4 FY25</t>
         </is>
       </c>
       <c r="C62" s="16" t="n">
-        <v>7263.916692435499</v>
+        <v>0.3348486413885732</v>
       </c>
       <c r="D62" s="16" t="n">
-        <v>6684.471401746357</v>
+        <v>0.4466637207247018</v>
       </c>
       <c r="E62" s="16" t="n">
-        <v>7893.591361742989</v>
+        <v>2.673797692889002</v>
       </c>
       <c r="F62" s="16" t="n">
-        <v>6396.68375475038</v>
+        <v>9.350243040212121</v>
       </c>
       <c r="G62" s="16" t="n">
-        <v>8248.725079688129</v>
+        <v>-0.7533697041211487</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v/>
+        <v>6.813126155328705</v>
       </c>
       <c r="I62" s="16" t="n">
-        <v/>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+        <v>-0.2349226231175515</v>
+      </c>
+      <c r="J62" s="16" t="n">
+        <v>5.824833828090004</v>
+      </c>
+      <c r="K62" s="16" t="n">
+        <v>-3.151036135201003</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2027Q1</t>
+          <t>2025Q4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Q2 FY27</t>
+          <t>Q1 FY26</t>
         </is>
       </c>
       <c r="C63" s="16" t="n">
-        <v>7263.916692435499</v>
+        <v>0.3591011719169982</v>
       </c>
       <c r="D63" s="16" t="n">
-        <v>6684.471401746357</v>
+        <v>0.5604339221578831</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>7893.591361742989</v>
+        <v>6.689337970920595</v>
       </c>
       <c r="F63" s="16" t="n">
-        <v>6396.68375475038</v>
+        <v>17.60040220545417</v>
       </c>
       <c r="G63" s="16" t="n">
-        <v>8248.725079688129</v>
+        <v>-0.9735725950081258</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v/>
+        <v>6.813126155328705</v>
       </c>
       <c r="I63" s="16" t="n">
-        <v/>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+        <v>-0.2349226231175515</v>
+      </c>
+      <c r="J63" s="16" t="n">
+        <v>5.604630937203028</v>
+      </c>
+      <c r="K63" s="16" t="n">
+        <v>1.084707033717566</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2027Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Q3 FY27</t>
+          <t>Q2 FY26</t>
         </is>
       </c>
       <c r="C64" s="16" t="n">
-        <v>7263.916692435499</v>
+        <v>0.3652369357557595</v>
       </c>
       <c r="D64" s="16" t="n">
-        <v>6684.471401746357</v>
+        <v>0.7441324392288349</v>
       </c>
       <c r="E64" s="16" t="n">
-        <v>7893.591361742989</v>
+        <v>8.085251199805665</v>
       </c>
       <c r="F64" s="16" t="n">
-        <v>6396.68375475038</v>
+        <v>37.6195024600746</v>
       </c>
       <c r="G64" s="16" t="n">
-        <v>8248.725079688129</v>
+        <v>-1.784133045244358</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v/>
+        <v>6.813126155328705</v>
       </c>
       <c r="I64" s="16" t="n">
-        <v/>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+        <v>-0.2349226231175515</v>
+      </c>
+      <c r="J64" s="16" t="n">
+        <v>4.794070486966795</v>
+      </c>
+      <c r="K64" s="16" t="n">
+        <v>3.291180712838869</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2027Q3</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Q4 FY27</t>
+          <t>Q3 FY26</t>
         </is>
       </c>
       <c r="C65" s="16" t="n">
-        <v>7263.916692435499</v>
+        <v>0.4011299435028248</v>
       </c>
       <c r="D65" s="16" t="n">
-        <v>6684.471401746357</v>
+        <v>0.8456194519490543</v>
       </c>
       <c r="E65" s="16" t="n">
-        <v>7893.591361742989</v>
+        <v>10.86605914888144</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>6396.68375475038</v>
+        <v>46.8455706115273</v>
       </c>
       <c r="G65" s="16" t="n">
-        <v>8248.725079688129</v>
+        <v>-2.216164561752094</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v/>
+        <v>6.813126155328705</v>
       </c>
       <c r="I65" s="16" t="n">
-        <v/>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+        <v>-0.2349226231175515</v>
+      </c>
+      <c r="J65" s="16" t="n">
+        <v>4.36203897045906</v>
+      </c>
+      <c r="K65" s="16" t="n">
+        <v>6.504020178422375</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>Daily return diagnostics since listing</t>
+          <t>SARIMA model selection by AICc (top 8)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>statistic</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>reading</t>
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>seasonal</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>aicc</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>aic</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>converged</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ADF, log price</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="n">
-        <v>0.2148338215487775</v>
+          <t>(0, 0, 1)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>(0, 0, 0)</t>
+        </is>
       </c>
       <c r="C70" s="16" t="n">
-        <v>0.9730814126546889</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Unit root not rejected → prices are non-stationary</t>
-        </is>
+        <v>-80.76052032075344</v>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>-81.68359724383036</v>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ADF, daily log returns</t>
-        </is>
-      </c>
-      <c r="B71" s="16" t="n">
-        <v>-18.78921724291201</v>
+          <t>(1, 0, 0)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>(0, 0, 0)</t>
+        </is>
       </c>
       <c r="C71" s="16" t="n">
-        <v>2.023593038964183e-30</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Stationary</t>
-        </is>
+        <v>-79.2250694206604</v>
+      </c>
+      <c r="D71" s="16" t="n">
+        <v>-80.14814634373732</v>
+      </c>
+      <c r="E71" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ljung-Box returns, lag 10</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="n">
-        <v>17.62246251584242</v>
+          <t>(1, 0, 1)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>(1, 0, 0)</t>
+        </is>
       </c>
       <c r="C72" s="16" t="n">
-        <v>0.0616760441367586</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>No significant autocorrelation</t>
-        </is>
+        <v>-79.04331614941496</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>-81.54331614941496</v>
+      </c>
+      <c r="E72" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ljung-Box returns, lag 20</t>
-        </is>
-      </c>
-      <c r="B73" s="16" t="n">
-        <v>29.08623275030963</v>
+          <t>(2, 0, 0)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>(0, 0, 0)</t>
+        </is>
       </c>
       <c r="C73" s="16" t="n">
-        <v>0.08607525732236759</v>
+        <v>-78.00979528579686</v>
       </c>
       <c r="D73" s="16" t="n">
-        <v/>
+        <v>-79.60979528579685</v>
+      </c>
+      <c r="E73" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ljung-Box squared returns, lag 10</t>
-        </is>
-      </c>
-      <c r="B74" s="16" t="n">
-        <v>558.3026320471224</v>
+          <t>(2, 1, 0)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>(0, 0, 0)</t>
+        </is>
       </c>
       <c r="C74" s="16" t="n">
-        <v>1.49801657682419e-113</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Volatility clustering</t>
-        </is>
+        <v>-77.66229737274683</v>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>-78.58537429582375</v>
+      </c>
+      <c r="E74" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engle ARCH-LM, 5 lags</t>
-        </is>
-      </c>
-      <c r="B75" s="16" t="n">
-        <v>250.8131669365303</v>
+          <t>(2, 0, 0)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>(1, 0, 0)</t>
+        </is>
       </c>
       <c r="C75" s="16" t="n">
-        <v>3.678250573790924e-52</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>ARCH effects</t>
-        </is>
+        <v>-77.10192681009327</v>
+      </c>
+      <c r="D75" s="16" t="n">
+        <v>-79.60192681009327</v>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>(0, 1, 0)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>(1, 0, 0)</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="n">
+        <v>-76.84608108904516</v>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>-77.2905255334896</v>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>(1, 1, 1)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>(1, 0, 0)</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="n">
+        <v>-76.43902131534753</v>
+      </c>
+      <c r="D77" s="16" t="n">
+        <v>-78.03902131534753</v>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>One-step rolling backtest, last 8 pre-Juniper quarters ($m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>arima</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>random_walk</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>seasonal_naive</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="n">
+        <v>7001.999999999995</v>
+      </c>
+      <c r="C82" s="16" t="n">
+        <v>6979.352717584006</v>
+      </c>
+      <c r="D82" s="16" t="n">
+        <v>6972.999999999995</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>6950.999999999997</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B83" s="16" t="n">
+        <v>7350.999999999995</v>
+      </c>
+      <c r="C83" s="16" t="n">
+        <v>7188.721388372651</v>
+      </c>
+      <c r="D83" s="16" t="n">
+        <v>7001.999999999995</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>7870.999999999994</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2023Q4</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="n">
+        <v>6754.999999999996</v>
+      </c>
+      <c r="C84" s="16" t="n">
+        <v>7288.72706993437</v>
+      </c>
+      <c r="D84" s="16" t="n">
+        <v>7350.999999999995</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>7809.000000000002</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="n">
+        <v>7204.000000000001</v>
+      </c>
+      <c r="C85" s="16" t="n">
+        <v>6814.331107889596</v>
+      </c>
+      <c r="D85" s="16" t="n">
+        <v>6754.999999999996</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>6972.999999999995</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="n">
+        <v>7709.999999999999</v>
+      </c>
+      <c r="C86" s="16" t="n">
+        <v>7398.184677051378</v>
+      </c>
+      <c r="D86" s="16" t="n">
+        <v>7204.000000000001</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>7001.999999999995</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="n">
+        <v>8458.000000000005</v>
+      </c>
+      <c r="C87" s="16" t="n">
+        <v>7360.645997958367</v>
+      </c>
+      <c r="D87" s="16" t="n">
+        <v>7709.999999999999</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>7350.999999999995</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2024Q4</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="n">
+        <v>7854.000000000006</v>
+      </c>
+      <c r="C88" s="16" t="n">
+        <v>7872.81529545054</v>
+      </c>
+      <c r="D88" s="16" t="n">
+        <v>8458.000000000005</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>6754.999999999996</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="n">
+        <v>7626.999999999999</v>
+      </c>
+      <c r="C89" s="16" t="n">
+        <v>7235.230854923676</v>
+      </c>
+      <c r="D89" s="16" t="n">
+        <v>7854.000000000006</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>7204.000000000001</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>Backtest accuracy: MAPE and Diebold-Mariano tests vs ARIMA (absolute errors, t-distribution)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="18" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>mape</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>dm_stat</t>
+        </is>
+      </c>
+      <c r="D93" s="18" t="inlineStr">
+        <is>
+          <t>dm_p_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>arima</t>
+        </is>
+      </c>
+      <c r="B94" s="16" t="n">
+        <v>0.04779489234298767</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>random_walk</t>
+        </is>
+      </c>
+      <c r="B95" s="16" t="n">
+        <v>0.05786348034052759</v>
+      </c>
+      <c r="C95" s="16" t="n">
+        <v>-0.8247341688051512</v>
+      </c>
+      <c r="D95" s="16" t="n">
+        <v>0.4367205786651854</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>seasonal_naive</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="n">
+        <v>0.08552759454186624</v>
+      </c>
+      <c r="C96" s="16" t="n">
+        <v>-2.049273245346905</v>
+      </c>
+      <c r="D96" s="16" t="n">
+        <v>0.0796157491410943</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>FY26 attribution under eight alternative no-structural-change baselines ($m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>fy26_counterfactual</t>
+        </is>
+      </c>
+      <c r="D100" s="18" t="inlineStr">
+        <is>
+          <t>fy26_excess</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>juniper_share_of_excess</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>quarters_above_95</t>
+        </is>
+      </c>
+      <c r="G100" s="18" t="inlineStr">
+        <is>
+          <t>quarters_with_actuals</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SARIMA(0,0,1)(0,0,0)[4]</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>AICc -80.8</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="n">
+        <v>29055.666769742</v>
+      </c>
+      <c r="D101" s="16" t="n">
+        <v>17444.333230258</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>0.3263279653829229</v>
+      </c>
+      <c r="F101" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G101" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SARIMA(1,0,0)(0,0,0)[4]</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>AICc -79.2</t>
+        </is>
+      </c>
+      <c r="C102" s="16" t="n">
+        <v>29216.99748816205</v>
+      </c>
+      <c r="D102" s="16" t="n">
+        <v>17283.00251183795</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>0.3293741215736497</v>
+      </c>
+      <c r="F102" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G102" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SARIMA(1,0,1)(1,0,0)[4]</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>AICc -79.0</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="n">
+        <v>29667.4070937419</v>
+      </c>
+      <c r="D103" s="16" t="n">
+        <v>16832.5929062581</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>0.3381875746769467</v>
+      </c>
+      <c r="F103" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G103" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SARIMA(2,0,0)(0,0,0)[4]</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AICc -78.0</t>
+        </is>
+      </c>
+      <c r="C104" s="16" t="n">
+        <v>28977.66020778317</v>
+      </c>
+      <c r="D104" s="16" t="n">
+        <v>17522.33979221683</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>0.3248752071923846</v>
+      </c>
+      <c r="F104" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SARIMA(2,1,0)(0,0,0)[4]</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>AICc -77.7</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="n">
+        <v>31537.67143208372</v>
+      </c>
+      <c r="D105" s="16" t="n">
+        <v>14962.32856791628</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>0.3804604172841381</v>
+      </c>
+      <c r="F105" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Random walk with drift</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>last level plus mean quarterly change</t>
+        </is>
+      </c>
+      <c r="C106" s="16" t="n">
+        <v>30478.93181613827</v>
+      </c>
+      <c r="D106" s="16" t="n">
+        <v>16021.06818386173</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0.3553179916072028</v>
+      </c>
+      <c r="G106" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Linear trend in log revenue</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>OLS trend on the fit sample</t>
+        </is>
+      </c>
+      <c r="C107" s="16" t="n">
+        <v>29552.98222657347</v>
+      </c>
+      <c r="D107" s="16" t="n">
+        <v>16947.01777342653</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>0.3359041600474359</v>
+      </c>
+      <c r="G107" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Seasonal naive</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>same quarter a year earlier</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="n">
+        <v>31649.00000000001</v>
+      </c>
+      <c r="D108" s="16" t="n">
+        <v>14850.99999999999</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>0.3833124887544145</v>
+      </c>
+      <c r="G108" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="inlineStr">
+        <is>
+          <t>Counterfactual forecast vs actual ($m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="18" t="inlineStr">
+        <is>
+          <t>calendar_quarter</t>
+        </is>
+      </c>
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t>fiscal_quarter</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>forecast</t>
+        </is>
+      </c>
+      <c r="D112" s="18" t="inlineStr">
+        <is>
+          <t>lo80</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="inlineStr">
+        <is>
+          <t>hi80</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>lo95</t>
+        </is>
+      </c>
+      <c r="G112" s="18" t="inlineStr">
+        <is>
+          <t>hi95</t>
+        </is>
+      </c>
+      <c r="H112" s="18" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="I112" s="18" t="inlineStr">
+        <is>
+          <t>actual_vs_forecast</t>
+        </is>
+      </c>
+      <c r="J112" s="18" t="inlineStr">
+        <is>
+          <t>outside_95</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Q3 FY25</t>
+        </is>
+      </c>
+      <c r="C113" s="16" t="n">
+        <v>7478.837167330837</v>
+      </c>
+      <c r="D113" s="16" t="n">
+        <v>6963.582091932272</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>8032.21741871197</v>
+      </c>
+      <c r="F113" s="16" t="n">
+        <v>6705.351696791737</v>
+      </c>
+      <c r="G113" s="16" t="n">
+        <v>8341.546857596002</v>
+      </c>
+      <c r="H113" s="16" t="n">
+        <v>9135.999999999998</v>
+      </c>
+      <c r="I113" s="16" t="n">
+        <v>0.2215802798739894</v>
+      </c>
+      <c r="J113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Q4 FY25</t>
+        </is>
+      </c>
+      <c r="C114" s="16" t="n">
+        <v>7263.916692435499</v>
+      </c>
+      <c r="D114" s="16" t="n">
+        <v>6684.471401746357</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>7893.591361742989</v>
+      </c>
+      <c r="F114" s="16" t="n">
+        <v>6396.68375475038</v>
+      </c>
+      <c r="G114" s="16" t="n">
+        <v>8248.725079688129</v>
+      </c>
+      <c r="H114" s="16" t="n">
+        <v>9679.000000000007</v>
+      </c>
+      <c r="I114" s="16" t="n">
+        <v>0.3324767353237308</v>
+      </c>
+      <c r="J114" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Q1 FY26</t>
+        </is>
+      </c>
+      <c r="C115" s="16" t="n">
+        <v>7263.916692435499</v>
+      </c>
+      <c r="D115" s="16" t="n">
+        <v>6684.471401746357</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>7893.591361742989</v>
+      </c>
+      <c r="F115" s="16" t="n">
+        <v>6396.68375475038</v>
+      </c>
+      <c r="G115" s="16" t="n">
+        <v>8248.725079688129</v>
+      </c>
+      <c r="H115" s="16" t="n">
+        <v>9301.000000000004</v>
+      </c>
+      <c r="I115" s="16" t="n">
+        <v>0.2804386935888023</v>
+      </c>
+      <c r="J115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Q2 FY26</t>
+        </is>
+      </c>
+      <c r="C116" s="16" t="n">
+        <v>7263.916692435499</v>
+      </c>
+      <c r="D116" s="16" t="n">
+        <v>6684.471401746357</v>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v>7893.591361742989</v>
+      </c>
+      <c r="F116" s="16" t="n">
+        <v>6396.68375475038</v>
+      </c>
+      <c r="G116" s="16" t="n">
+        <v>8248.725079688129</v>
+      </c>
+      <c r="H116" s="16" t="n">
+        <v>10678</v>
+      </c>
+      <c r="I116" s="16" t="n">
+        <v>0.4700058456231821</v>
+      </c>
+      <c r="J116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Q3 FY26</t>
+        </is>
+      </c>
+      <c r="C117" s="16" t="n">
+        <v>7263.916692435499</v>
+      </c>
+      <c r="D117" s="16" t="n">
+        <v>6684.471401746357</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>7893.591361742989</v>
+      </c>
+      <c r="F117" s="16" t="n">
+        <v>6396.68375475038</v>
+      </c>
+      <c r="G117" s="16" t="n">
+        <v>8248.725079688129</v>
+      </c>
+      <c r="H117" s="16" t="n">
+        <v>12213</v>
+      </c>
+      <c r="I117" s="16" t="n">
+        <v>0.6813243484356557</v>
+      </c>
+      <c r="J117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Q4 FY26</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="n">
+        <v>7263.916692435499</v>
+      </c>
+      <c r="D118" s="16" t="n">
+        <v>6684.471401746357</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>7893.591361742989</v>
+      </c>
+      <c r="F118" s="16" t="n">
+        <v>6396.68375475038</v>
+      </c>
+      <c r="G118" s="16" t="n">
+        <v>8248.725079688129</v>
+      </c>
+      <c r="J118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026Q4</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Q1 FY27</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="n">
+        <v>7263.916692435499</v>
+      </c>
+      <c r="D119" s="16" t="n">
+        <v>6684.471401746357</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>7893.591361742989</v>
+      </c>
+      <c r="F119" s="16" t="n">
+        <v>6396.68375475038</v>
+      </c>
+      <c r="G119" s="16" t="n">
+        <v>8248.725079688129</v>
+      </c>
+      <c r="J119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2027Q1</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Q2 FY27</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="n">
+        <v>7263.916692435499</v>
+      </c>
+      <c r="D120" s="16" t="n">
+        <v>6684.471401746357</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>7893.591361742989</v>
+      </c>
+      <c r="F120" s="16" t="n">
+        <v>6396.68375475038</v>
+      </c>
+      <c r="G120" s="16" t="n">
+        <v>8248.725079688129</v>
+      </c>
+      <c r="J120" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2027Q2</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Q3 FY27</t>
+        </is>
+      </c>
+      <c r="C121" s="16" t="n">
+        <v>7263.916692435499</v>
+      </c>
+      <c r="D121" s="16" t="n">
+        <v>6684.471401746357</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>7893.591361742989</v>
+      </c>
+      <c r="F121" s="16" t="n">
+        <v>6396.68375475038</v>
+      </c>
+      <c r="G121" s="16" t="n">
+        <v>8248.725079688129</v>
+      </c>
+      <c r="J121" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2027Q3</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Q4 FY27</t>
+        </is>
+      </c>
+      <c r="C122" s="16" t="n">
+        <v>7263.916692435499</v>
+      </c>
+      <c r="D122" s="16" t="n">
+        <v>6684.471401746357</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>7893.591361742989</v>
+      </c>
+      <c r="F122" s="16" t="n">
+        <v>6396.68375475038</v>
+      </c>
+      <c r="G122" s="16" t="n">
+        <v>8248.725079688129</v>
+      </c>
+      <c r="J122" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="inlineStr">
+        <is>
+          <t>Daily return diagnostics since listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="18" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B126" s="18" t="inlineStr">
+        <is>
+          <t>statistic</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="D126" s="18" t="inlineStr">
+        <is>
+          <t>reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ADF, log price</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="n">
+        <v>0.2148338215487775</v>
+      </c>
+      <c r="C127" s="16" t="n">
+        <v>0.9730814126546889</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Unit root not rejected → prices are non-stationary</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ADF, daily log returns</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="n">
+        <v>-18.78921724291201</v>
+      </c>
+      <c r="C128" s="16" t="n">
+        <v>2.023593038964183e-30</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Stationary</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Ljung-Box returns, lag 10</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="n">
+        <v>17.62246251584242</v>
+      </c>
+      <c r="C129" s="16" t="n">
+        <v>0.0616760441367586</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>No significant autocorrelation</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Ljung-Box returns, lag 20</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="n">
+        <v>29.08623275030963</v>
+      </c>
+      <c r="C130" s="16" t="n">
+        <v>0.08607525732236759</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Ljung-Box squared returns, lag 10</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="n">
+        <v>558.3026320471224</v>
+      </c>
+      <c r="C131" s="16" t="n">
+        <v>1.49801657682419e-113</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Volatility clustering</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Engle ARCH-LM, 5 lags</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="n">
+        <v>250.8131669365303</v>
+      </c>
+      <c r="C132" s="16" t="n">
+        <v>3.678250573790924e-52</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ARCH effects</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>Jarque-Bera normality</t>
         </is>
       </c>
-      <c r="B76" s="16" t="n">
+      <c r="B133" s="16" t="n">
         <v>5500.731103111989</v>
       </c>
-      <c r="C76" s="16" t="n">
+      <c r="C133" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>Non-normal (fat tails)</t>
         </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="inlineStr">
+        <is>
+          <t>Tests of descriptive claims used in the pitch</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="18" t="inlineStr">
+        <is>
+          <t>claim</t>
+        </is>
+      </c>
+      <c r="B137" s="18" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D137" s="18" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="E137" s="18" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="F137" s="18" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+      <c r="G137" s="18" t="inlineStr">
+        <is>
+          <t>ci_low</t>
+        </is>
+      </c>
+      <c r="H137" s="18" t="inlineStr">
+        <is>
+          <t>ci_high</t>
+        </is>
+      </c>
+      <c r="I137" s="18" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Earnings days move the stock more than other days</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2024-03-01 to 2026-09-11</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Permutation test on mean absolute day-0 return (20,000 draws); Mann-Whitney p=0.0003</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>0.0667620192874311</v>
+      </c>
+      <c r="F138" s="16" t="n">
+        <v>0.0199129236046465</v>
+      </c>
+      <c r="I138" s="16" t="n">
+        <v>4.999750012499375e-05</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>HPE's returns correlate more with Dell than with the S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1Y: 2025-09-12 to 2026-09-11</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Stationary block bootstrap of the correlation gap (5,000 draws, 20-day blocks)</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>251</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>0.6557101051629635</v>
+      </c>
+      <c r="F139" s="16" t="n">
+        <v>0.4678005860720897</v>
+      </c>
+      <c r="G139" s="16" t="n">
+        <v>0.08897653719529459</v>
+      </c>
+      <c r="H139" s="16" t="n">
+        <v>0.2842767214731474</v>
+      </c>
+      <c r="I139" s="16" t="n">
+        <v>0.0007998400319935999</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>HPE's returns correlate more with Dell than with the S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>3Y: 2023-09-12 to 2026-09-11</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Stationary block bootstrap of the correlation gap (5,000 draws, 20-day blocks)</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>753</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>0.5940910542364788</v>
+      </c>
+      <c r="F140" s="16" t="n">
+        <v>0.5331344397940082</v>
+      </c>
+      <c r="G140" s="16" t="n">
+        <v>-0.0352888803707311</v>
+      </c>
+      <c r="H140" s="16" t="n">
+        <v>0.1546737546434476</v>
+      </c>
+      <c r="I140" s="16" t="n">
+        <v>0.2059588082383523</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="inlineStr">
+        <is>
+          <t>Practitioner Q&amp;A 2: revenue elasticity to hyperscaler capex (lags 0–4 summed), HPE with Juniper dummy, Dell − HPE gap test</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="18" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B144" s="18" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="D144" s="18" t="inlineStr">
+        <is>
+          <t>sum_of_lags</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="inlineStr">
+        <is>
+          <t>sum_p</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="G144" s="18" t="inlineStr">
+        <is>
+          <t>best_single_lag</t>
+        </is>
+      </c>
+      <c r="H144" s="18" t="inlineStr">
+        <is>
+          <t>best_lag_coef</t>
+        </is>
+      </c>
+      <c r="I144" s="18" t="inlineStr">
+        <is>
+          <t>best_lag_p</t>
+        </is>
+      </c>
+      <c r="J144" s="18" t="inlineStr">
+        <is>
+          <t>juniper_controlled_sum</t>
+        </is>
+      </c>
+      <c r="K144" s="18" t="inlineStr">
+        <is>
+          <t>juniper_controlled_p</t>
+        </is>
+      </c>
+      <c r="L144" s="18" t="inlineStr">
+        <is>
+          <t>gap_vs_hpe_sum</t>
+        </is>
+      </c>
+      <c r="M144" s="18" t="inlineStr">
+        <is>
+          <t>gap_vs_hpe_p</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>DLR</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2018Q2–2026Q2</t>
+        </is>
+      </c>
+      <c r="D145" s="16" t="n">
+        <v>0.0588301994392499</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>0.5595179059787644</v>
+      </c>
+      <c r="F145" s="16" t="n">
+        <v>0.0894795768392896</v>
+      </c>
+      <c r="G145" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" s="16" t="n">
+        <v>0.103759342563621</v>
+      </c>
+      <c r="I145" s="16" t="n">
+        <v>0.0933533191735974</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2018Q2–2026Q2</t>
+        </is>
+      </c>
+      <c r="D146" s="16" t="n">
+        <v>0.4082248322211891</v>
+      </c>
+      <c r="E146" s="16" t="n">
+        <v>0.0220677121761258</v>
+      </c>
+      <c r="F146" s="16" t="n">
+        <v>0.4451560604781566</v>
+      </c>
+      <c r="G146" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="16" t="n">
+        <v>0.287519322549574</v>
+      </c>
+      <c r="I146" s="16" t="n">
+        <v>0.010367702948633</v>
+      </c>
+      <c r="J146" s="16" t="n">
+        <v>0.09403667062667879</v>
+      </c>
+      <c r="K146" s="16" t="n">
+        <v>0.4512065580242902</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2018Q2–2026Q2</t>
+        </is>
+      </c>
+      <c r="D147" s="16" t="n">
+        <v>0.8430410443390439</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>0.0001137970340467</v>
+      </c>
+      <c r="F147" s="16" t="n">
+        <v>0.548987137153219</v>
+      </c>
+      <c r="G147" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" s="16" t="n">
+        <v>0.5277458006697319</v>
+      </c>
+      <c r="I147" s="16" t="n">
+        <v>0.0018624312312751</v>
+      </c>
+      <c r="L147" s="16" t="n">
+        <v>0.4348162121178547</v>
+      </c>
+      <c r="M147" s="16" t="n">
+        <v>0.0038056922405213</v>
       </c>
     </row>
   </sheetData>
